--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486493_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486493_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9171</v>
+        <v>5.8383</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9512</v>
+        <v>3.0882</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9659</v>
+        <v>2.7501</v>
       </c>
       <c r="G2" t="n">
         <v>2.5911</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9557</v>
+        <v>0.8769</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4747</v>
+        <v>0.6117</v>
       </c>
       <c r="U2" t="n">
-        <v>0.481</v>
+        <v>0.2653</v>
       </c>
       <c r="V2" t="n">
         <v>0.1952</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. ARAMBURU LAMY</t>
+          <t>A. SCARIOLO ARES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0382</v>
+        <v>0.8732</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0295</v>
+        <v>1.3327</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9913</v>
+        <v>-0.4596</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.3223</v>
+        <v>1.1693</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.6577</v>
+        <v>0.9398</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.6647</v>
+        <v>0.2295</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4758</v>
+        <v>1.4697</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1944</v>
+        <v>0.8577</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6702</v>
+        <v>0.612</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.7981</v>
+        <v>-0.3004</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4633</v>
+        <v>0.082</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.3348</v>
+        <v>-0.3825</v>
       </c>
       <c r="P3" t="n">
-        <v>3.2626</v>
+        <v>0.6525</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.2626</v>
+        <v>0.6525</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7074</v>
+        <v>-0.3836</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1633</v>
+        <v>-0.137</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4558</v>
+        <v>-0.2466</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3904</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. SCARIOLO ARES</t>
+          <t>J. ARAMBURU LAMY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7738</v>
+        <v>0.1886</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2642</v>
+        <v>1.2724</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4904</v>
+        <v>-1.0838</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1693</v>
+        <v>-3.3223</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9398</v>
+        <v>-1.6577</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2295</v>
+        <v>-1.6647</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4697</v>
+        <v>0.4758</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8577</v>
+        <v>-0.1944</v>
       </c>
       <c r="L4" t="n">
-        <v>0.612</v>
+        <v>0.6702</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3004</v>
+        <v>-3.7981</v>
       </c>
       <c r="N4" t="n">
-        <v>0.082</v>
+        <v>-1.4633</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3825</v>
+        <v>-2.3348</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6525</v>
+        <v>3.2626</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6525</v>
+        <v>3.2626</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.483</v>
+        <v>-0.1421</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2055</v>
+        <v>0.4062</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2775</v>
+        <v>-0.5483</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.3904</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5857</v>
+        <v>-0.232</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0607</v>
+        <v>-0.7687</v>
       </c>
       <c r="F5" t="n">
-        <v>0.475</v>
+        <v>0.5366</v>
       </c>
       <c r="G5" t="n">
         <v>1.788</v>
@@ -844,13 +844,13 @@
         <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4317</v>
+        <v>0.7853</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2776</v>
+        <v>0.5696</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1541</v>
+        <v>0.2157</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1952</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. SIQUIER COSTA</t>
+          <t>L. BRACEY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.181</v>
+        <v>-0.9021</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.168</v>
+        <v>-1.0235</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0129</v>
+        <v>0.1214</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3746</v>
+        <v>-1.1279</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9275</v>
+        <v>1.2197</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.447</v>
+        <v>-2.3475</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.4901</v>
+        <v>0.1225</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7451</v>
+        <v>1.5361</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7451</v>
+        <v>-1.4136</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1155</v>
+        <v>-1.2504</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1825</v>
+        <v>-0.3164</v>
       </c>
       <c r="O6" t="n">
-        <v>0.298</v>
+        <v>-0.9339</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2175</v>
+        <v>-0.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2175</v>
+        <v>-2.1751</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4111</v>
+        <v>0.161</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5396</v>
+        <v>-0.1009</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1285</v>
+        <v>0.262</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.9347</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. BRACEY</t>
+          <t>O. SIQUIER COSTA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6642</v>
+        <v>-1.4854</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5391</v>
+        <v>-1.5033</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1252</v>
+        <v>0.0179</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1279</v>
+        <v>-1.3746</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2197</v>
+        <v>-0.9275</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.3475</v>
+        <v>-0.447</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1225</v>
+        <v>-1.4901</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5361</v>
+        <v>-0.7451</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4136</v>
+        <v>-0.7451</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2504</v>
+        <v>0.1155</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3164</v>
+        <v>-0.1825</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9339</v>
+        <v>0.298</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.87</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1751</v>
+        <v>-0.2175</v>
       </c>
       <c r="R7" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6011</v>
+        <v>0.1067</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6165</v>
+        <v>0.2043</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0154</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9347</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9334</v>
+        <v>-2.3186</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6033</v>
+        <v>-2.0192</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3302</v>
+        <v>-0.2993</v>
       </c>
       <c r="G8" t="n">
         <v>-2.543</v>
@@ -1078,13 +1078,13 @@
         <v>1.9576</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0429</v>
+        <v>-0.4281</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3268</v>
+        <v>0.2572</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7161</v>
+        <v>-0.6853</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2685</v>
+        <v>-3.3927</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6478</v>
+        <v>-2.8028</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6208</v>
+        <v>-0.5899</v>
       </c>
       <c r="G9" t="n">
         <v>-1.5991</v>
@@ -1156,13 +1156,13 @@
         <v>1.9576</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3219</v>
+        <v>-0.4461</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.1634</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3135</v>
+        <v>-0.2827</v>
       </c>
       <c r="V9" t="n">
         <v>-1.13</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7884</v>
+        <v>-3.6128</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3674</v>
+        <v>-4.0069</v>
       </c>
       <c r="F10" t="n">
-        <v>0.579</v>
+        <v>0.3941</v>
       </c>
       <c r="G10" t="n">
         <v>-4.0076</v>
@@ -1234,13 +1234,13 @@
         <v>2.6101</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2158</v>
+        <v>-0.0403</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1214</v>
+        <v>0.2392</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0945</v>
+        <v>-0.2794</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.45</v>
+        <v>-4.4624</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5394</v>
+        <v>-4.5827</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0895</v>
+        <v>0.1203</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1933</v>
@@ -1312,13 +1312,13 @@
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1131</v>
+        <v>0.1006</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2776</v>
+        <v>0.2343</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1645</v>
+        <v>-0.1337</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9347</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0864</v>
+        <v>-4.5593</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1664</v>
+        <v>-2.7626</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.92</v>
+        <v>-1.7967</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9648</v>
@@ -1390,13 +1390,13 @@
         <v>1.305</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5773</v>
+        <v>-1.0503</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9589</v>
+        <v>-0.5552</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.4951</v>
       </c>
       <c r="V12" t="n">
         <v>-1.6743</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.7832</v>
+        <v>-6.8072</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.1754</v>
+        <v>-6.1069</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6078</v>
+        <v>-0.7003</v>
       </c>
       <c r="G13" t="n">
         <v>-2.6759</v>
@@ -1468,13 +1468,13 @@
         <v>2.3926</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.7381</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3389</v>
+        <v>-0.2704</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3753</v>
+        <v>-0.4678</v>
       </c>
       <c r="V13" t="n">
         <v>0.7395</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-22.0117</v>
+        <v>-20.8724</v>
       </c>
       <c r="E14" t="n">
-        <v>-21.0226</v>
+        <v>-19.8833</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9892000000000002</v>
+        <v>-0.9891999999999997</v>
       </c>
       <c r="G14" t="n">
         <v>-15.2601</v>
       </c>
       <c r="H14" t="n">
-        <v>-8.454900000000002</v>
+        <v>-8.4549</v>
       </c>
       <c r="I14" t="n">
         <v>-6.805099999999999</v>
@@ -1537,7 +1537,7 @@
         <v>-7.2037</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.175000000000001</v>
+        <v>-2.175</v>
       </c>
       <c r="Q14" t="n">
         <v>-21.7507</v>
@@ -1546,13 +1546,13 @@
         <v>19.5756</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.3372</v>
+        <v>-1.1981</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1564</v>
+        <v>1.2956</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.4936</v>
+        <v>-2.4935</v>
       </c>
       <c r="V14" t="n">
         <v>-2.239399999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>Y. BARRUETA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.6999</v>
+        <v>7.0194</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0887</v>
+        <v>5.7584</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6112</v>
+        <v>1.261</v>
       </c>
       <c r="G15" t="n">
-        <v>3.268</v>
+        <v>3.8219</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6918</v>
+        <v>3.0626</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.7594</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3262</v>
+        <v>4.1161</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5612</v>
+        <v>2.7009</v>
       </c>
       <c r="L15" t="n">
-        <v>0.765</v>
+        <v>1.4152</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0583</v>
+        <v>-0.2942</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1306</v>
+        <v>0.3617</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1889</v>
+        <v>-0.6558</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>1.5225</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1751</v>
+        <v>2.6101</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1274</v>
+        <v>0.545</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1773</v>
+        <v>0.4699</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0499</v>
+        <v>0.0751</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3045</v>
+        <v>1.13</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7602</v>
+        <v>2.2599</v>
       </c>
       <c r="X15" t="n">
-        <v>0.5443</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Y. BARRUETA</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.3649</v>
+        <v>5.5714</v>
       </c>
       <c r="E16" t="n">
-        <v>6.0937</v>
+        <v>2.9653</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2712</v>
+        <v>2.6061</v>
       </c>
       <c r="G16" t="n">
-        <v>3.8219</v>
+        <v>3.268</v>
       </c>
       <c r="H16" t="n">
-        <v>3.0626</v>
+        <v>2.6918</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7594</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1161</v>
+        <v>3.3262</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7009</v>
+        <v>2.5612</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4152</v>
+        <v>0.765</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2942</v>
+        <v>-0.0583</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3617</v>
+        <v>0.1306</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6558</v>
+        <v>-0.1889</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5225</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R16" t="n">
-        <v>2.6101</v>
+        <v>2.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8904</v>
+        <v>0.9989</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8051</v>
+        <v>1.0539</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0853</v>
+        <v>-0.055</v>
       </c>
       <c r="V16" t="n">
-        <v>1.13</v>
+        <v>1.3045</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2599</v>
+        <v>0.7602</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.13</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. KRAVIC</t>
+          <t>L. WESTERMANN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2614</v>
+        <v>5.215</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3641</v>
+        <v>2.6373</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8972</v>
+        <v>2.5777</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8248</v>
+        <v>6.0256</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2232</v>
+        <v>1.615</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3984</v>
+        <v>4.4106</v>
       </c>
       <c r="J17" t="n">
-        <v>2.5286</v>
+        <v>5.4703</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3756</v>
+        <v>1.7004</v>
       </c>
       <c r="L17" t="n">
-        <v>0.153</v>
+        <v>3.77</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7038</v>
+        <v>0.5553</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1523</v>
+        <v>-0.0854</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5514</v>
+        <v>0.6407</v>
       </c>
       <c r="P17" t="n">
-        <v>0.435</v>
+        <v>-1.305</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.305</v>
+        <v>-3.2626</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7401</v>
+        <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8923</v>
+        <v>0.2992</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5756</v>
+        <v>0.2343</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3166</v>
+        <v>0.0649</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1093</v>
+        <v>0.1952</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.1952</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5443</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.2587</v>
+        <v>4.3627</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3481</v>
+        <v>2.2363</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9106</v>
+        <v>2.1264</v>
       </c>
       <c r="G18" t="n">
         <v>2.2822</v>
@@ -1858,13 +1858,13 @@
         <v>1.9576</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2364</v>
+        <v>0.3404</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5071</v>
+        <v>0.3954</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2708</v>
+        <v>-0.055</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. WESTERMANN</t>
+          <t>D. KRAVIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.0628</v>
+        <v>4.0327</v>
       </c>
       <c r="E19" t="n">
-        <v>1.855</v>
+        <v>2.1406</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2078</v>
+        <v>1.8921</v>
       </c>
       <c r="G19" t="n">
-        <v>6.0256</v>
+        <v>1.8248</v>
       </c>
       <c r="H19" t="n">
-        <v>1.615</v>
+        <v>2.2232</v>
       </c>
       <c r="I19" t="n">
-        <v>4.4106</v>
+        <v>-0.3984</v>
       </c>
       <c r="J19" t="n">
-        <v>5.4703</v>
+        <v>2.5286</v>
       </c>
       <c r="K19" t="n">
-        <v>1.7004</v>
+        <v>2.3756</v>
       </c>
       <c r="L19" t="n">
-        <v>3.77</v>
+        <v>0.153</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5553</v>
+        <v>-0.7038</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0854</v>
+        <v>-0.1523</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6407</v>
+        <v>-0.5514</v>
       </c>
       <c r="P19" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-1.305</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-3.2626</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.9576</v>
+        <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.853</v>
+        <v>0.6636</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.548</v>
+        <v>0.3521</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.305</v>
+        <v>0.3115</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1952</v>
+        <v>1.1093</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1952</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ETXEGUREN GONZALEZ</t>
+          <t>A. BARCELLO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1434</v>
+        <v>1.9425</v>
       </c>
       <c r="E20" t="n">
-        <v>0.588</v>
+        <v>-0.5438</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5555</v>
+        <v>2.4862</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5919</v>
+        <v>0.1326</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3193</v>
+        <v>-0.7511</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2726</v>
+        <v>0.8837</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6667</v>
+        <v>0.4292</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0547</v>
+        <v>-1.0458</v>
       </c>
       <c r="L20" t="n">
-        <v>0.612</v>
+        <v>1.475</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9251</v>
+        <v>-0.2966</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2645</v>
+        <v>0.2947</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6606</v>
+        <v>-0.5913</v>
       </c>
       <c r="P20" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R20" t="n">
-        <v>0.435</v>
+        <v>3.0451</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0513</v>
+        <v>-0.1902</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.274</v>
+        <v>0.0721</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3253</v>
+        <v>-0.2623</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9347</v>
+        <v>1.13</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. DE SOUSA ANJO BRITO</t>
+          <t>A. ETXEGUREN GONZALEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9226</v>
+        <v>1.1627</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7753</v>
+        <v>0.6997</v>
       </c>
       <c r="F21" t="n">
-        <v>2.698</v>
+        <v>0.463</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5857</v>
+        <v>1.5919</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4318</v>
+        <v>0.3193</v>
       </c>
       <c r="I21" t="n">
-        <v>2.1539</v>
+        <v>1.2726</v>
       </c>
       <c r="J21" t="n">
-        <v>1.679</v>
+        <v>0.6667</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1857</v>
+        <v>0.0547</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4933</v>
+        <v>0.612</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9067</v>
+        <v>0.9251</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2461</v>
+        <v>0.2645</v>
       </c>
       <c r="O21" t="n">
         <v>0.6606</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.1751</v>
+        <v>0.435</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4801</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3168</v>
+        <v>0.0706</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1694</v>
+        <v>-0.1622</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4862</v>
+        <v>0.2328</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1952</v>
+        <v>-0.9347</v>
       </c>
       <c r="W21" t="n">
         <v>0.1952</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. BARCELLO</t>
+          <t>D. DE SOUSA ANJO BRITO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3497</v>
+        <v>1.0229</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4378</v>
+        <v>-1.5518</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7875</v>
+        <v>2.5747</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1326</v>
+        <v>2.5857</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7511</v>
+        <v>0.4318</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8837</v>
+        <v>2.1539</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4292</v>
+        <v>1.679</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.0458</v>
+        <v>0.1857</v>
       </c>
       <c r="L22" t="n">
-        <v>1.475</v>
+        <v>1.4933</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2966</v>
+        <v>0.9067</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2947</v>
+        <v>0.2461</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5913</v>
+        <v>0.6606</v>
       </c>
       <c r="P22" t="n">
-        <v>0.87</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1751</v>
+        <v>-3.4801</v>
       </c>
       <c r="R22" t="n">
-        <v>3.0451</v>
+        <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.783</v>
+        <v>0.417</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.822</v>
+        <v>0.0541</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.961</v>
+        <v>0.3629</v>
       </c>
       <c r="V22" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. MUNNINGS</t>
+          <t>A. GALAN POZO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4939</v>
+        <v>-0.315</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8589</v>
+        <v>-1.6948</v>
       </c>
       <c r="F23" t="n">
-        <v>1.365</v>
+        <v>1.3798</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-1.715</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2891</v>
+        <v>0.4532</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1992</v>
+        <v>-2.1683</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1001</v>
+        <v>-1.6543</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1277</v>
+        <v>0.3896</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.2279</v>
+        <v>-2.0439</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0102</v>
+        <v>-0.0607</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4169</v>
+        <v>0.0636</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4271</v>
+        <v>-0.1243</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.3926</v>
+        <v>-1.0875</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7401</v>
+        <v>2.3926</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8136</v>
+        <v>0.2902</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4386</v>
+        <v>-0.0829</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3749</v>
+        <v>0.3731</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.1952</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.7602</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. GALAN POZO</t>
+          <t>T. MUNNINGS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.9754</v>
+        <v>-0.7174</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3654</v>
+        <v>-2.0824</v>
       </c>
       <c r="F24" t="n">
-        <v>1.39</v>
+        <v>1.365</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.715</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4532</v>
+        <v>-0.2891</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.1683</v>
+        <v>0.1992</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.6543</v>
+        <v>-0.1001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3896</v>
+        <v>0.1277</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.0439</v>
+        <v>-0.2279</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0607</v>
+        <v>0.0102</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0636</v>
+        <v>-0.4169</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1243</v>
+        <v>0.4271</v>
       </c>
       <c r="P24" t="n">
-        <v>1.305</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0875</v>
+        <v>-2.3926</v>
       </c>
       <c r="R24" t="n">
-        <v>2.3926</v>
+        <v>1.7401</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3701</v>
+        <v>0.59</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.2151</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3833</v>
+        <v>0.3749</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1952</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.3252</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.4726</v>
+        <v>-2.1194</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.5724</v>
+        <v>-1.4606</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9003</v>
+        <v>-0.6588000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-1.2553</v>
@@ -2404,13 +2404,13 @@
         <v>0.435</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5224</v>
+        <v>-0.1691</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.137</v>
+        <v>-0.0252</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3854</v>
+        <v>-0.1439</v>
       </c>
       <c r="V25" t="n">
         <v>-1.13</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.1098</v>
+        <v>-3.6757</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.3391</v>
+        <v>-5.1156</v>
       </c>
       <c r="F26" t="n">
-        <v>1.2293</v>
+        <v>1.44</v>
       </c>
       <c r="G26" t="n">
         <v>-3.2124</v>
@@ -2482,13 +2482,13 @@
         <v>1.9576</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4624</v>
+        <v>-0.0282</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3064</v>
+        <v>-0.0829</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.156</v>
+        <v>0.0547</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,22 +2515,22 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>22.0117</v>
+        <v>23.5018</v>
       </c>
       <c r="E27" t="n">
-        <v>3.988700000000001</v>
+        <v>3.988600000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>18.023</v>
+        <v>19.5132</v>
       </c>
       <c r="G27" t="n">
         <v>15.2601</v>
       </c>
       <c r="H27" t="n">
-        <v>8.455000000000002</v>
+        <v>8.455</v>
       </c>
       <c r="I27" t="n">
-        <v>6.805099999999999</v>
+        <v>6.805099999999998</v>
       </c>
       <c r="J27" t="n">
         <v>14.4447</v>
@@ -2539,7 +2539,7 @@
         <v>7.2409</v>
       </c>
       <c r="L27" t="n">
-        <v>7.203800000000001</v>
+        <v>7.203799999999999</v>
       </c>
       <c r="M27" t="n">
         <v>0.8152999999999999</v>
@@ -2548,7 +2548,7 @@
         <v>1.214</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.3985000000000004</v>
+        <v>-0.3985000000000002</v>
       </c>
       <c r="P27" t="n">
         <v>2.175</v>
@@ -2560,13 +2560,13 @@
         <v>21.7509</v>
       </c>
       <c r="S27" t="n">
-        <v>2.3373</v>
+        <v>3.8274</v>
       </c>
       <c r="T27" t="n">
-        <v>2.493399999999999</v>
+        <v>2.4937</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.1565</v>
+        <v>1.3337</v>
       </c>
       <c r="V27" t="n">
         <v>2.239300000000001</v>
@@ -2575,7 +2575,7 @@
         <v>6.6259</v>
       </c>
       <c r="X27" t="n">
-        <v>-4.386799999999999</v>
+        <v>-4.3868</v>
       </c>
     </row>
   </sheetData>
